--- a/Shiny/Datos limpios/pricing_semanal_maiz_2025.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_maiz_2025.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -2288,33 +2288,162 @@
         <v>45957</v>
       </c>
       <c r="D45">
-        <v>1510</v>
+        <v>373234.85</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>5158.69</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>2207.26</v>
       </c>
       <c r="G45">
-        <v>1510</v>
+        <v>376186.28</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>180008.45</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>178108.45</v>
       </c>
       <c r="L45">
-        <v>1510</v>
+        <v>554294.73</v>
       </c>
       <c r="M45" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2025</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D46">
+        <v>693828.79</v>
+      </c>
+      <c r="E46">
+        <v>14753.51</v>
+      </c>
+      <c r="F46">
+        <v>11412.73</v>
+      </c>
+      <c r="G46">
+        <v>697169.5700000001</v>
+      </c>
+      <c r="H46">
+        <v>171681.39</v>
+      </c>
+      <c r="I46">
+        <v>6065</v>
+      </c>
+      <c r="J46">
+        <v>710</v>
+      </c>
+      <c r="K46">
+        <v>177036.39</v>
+      </c>
+      <c r="L46">
+        <v>874205.9600000001</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2025</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D47">
+        <v>894388.11</v>
+      </c>
+      <c r="E47">
+        <v>4907.6</v>
+      </c>
+      <c r="F47">
+        <v>27747.65</v>
+      </c>
+      <c r="G47">
+        <v>871548.0599999999</v>
+      </c>
+      <c r="H47">
+        <v>143102.77</v>
+      </c>
+      <c r="I47">
+        <v>204.23</v>
+      </c>
+      <c r="J47">
+        <v>660</v>
+      </c>
+      <c r="K47">
+        <v>142647</v>
+      </c>
+      <c r="L47">
+        <v>1014195.06</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2025</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D48">
+        <v>276469.33</v>
+      </c>
+      <c r="E48">
+        <v>8578.219999999999</v>
+      </c>
+      <c r="F48">
+        <v>3805.43</v>
+      </c>
+      <c r="G48">
+        <v>281242.12</v>
+      </c>
+      <c r="H48">
+        <v>103695.6</v>
+      </c>
+      <c r="I48">
+        <v>153.25</v>
+      </c>
+      <c r="J48">
+        <v>630</v>
+      </c>
+      <c r="K48">
+        <v>103218.85</v>
+      </c>
+      <c r="L48">
+        <v>384460.97</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>MAIZ</t>
         </is>
